--- a/output/Datos Afip/Mis Comprobantes Emitidos - CUIT 23132146454.xlsx
+++ b/output/Datos Afip/Mis Comprobantes Emitidos - CUIT 23132146454.xlsx
@@ -199,8 +199,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18.2" customWidth="1"/>
     <col min="3" max="3" width="18.2" customWidth="1"/>
     <col min="4" max="4" width="15.600000000000001" customWidth="1"/>
     <col min="5" max="5" width="15.600000000000001" customWidth="1"/>
@@ -378,7 +378,108 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c t="inlineStr" r="A3">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B3">
+        <is>
+          <t>11 - Factura C</t>
+        </is>
+      </c>
+      <c r="C3" s="65">
+        <v>2</v>
+      </c>
+      <c r="D3" s="65">
+        <v>19</v>
+      </c>
+      <c r="E3" s="65">
+        <v>19</v>
+      </c>
+      <c r="F3" s="65">
+        <v>75404203971967</v>
+      </c>
+      <c t="inlineStr" r="G3">
+        <is>
+          <t>CUIT</t>
+        </is>
+      </c>
+      <c r="H3" s="65">
+        <v>20063465144</v>
+      </c>
+      <c t="inlineStr" r="I3">
+        <is>
+          <t>SENN CARLOS</t>
+        </is>
+      </c>
+      <c r="J3" s="65">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="K3">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="Z3" s="65">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="66">
+        <v>5485173.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c t="inlineStr" r="A4">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B4">
+        <is>
+          <t>11 - Factura C</t>
+        </is>
+      </c>
+      <c r="C4" s="65">
+        <v>2</v>
+      </c>
+      <c r="D4" s="65">
+        <v>20</v>
+      </c>
+      <c r="E4" s="65">
+        <v>20</v>
+      </c>
+      <c r="F4" s="65">
+        <v>75404970233447</v>
+      </c>
+      <c t="inlineStr" r="G4">
+        <is>
+          <t>CUIT</t>
+        </is>
+      </c>
+      <c r="H4" s="65">
+        <v>20270211985</v>
+      </c>
+      <c t="inlineStr" r="I4">
+        <is>
+          <t>CHAMORRO CARLOS IVAN</t>
+        </is>
+      </c>
+      <c r="J4" s="65">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="K4">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="Z4" s="65">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="65">
+        <v>2103333</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
